--- a/artfynd/A 33012-2021 artfynd.xlsx
+++ b/artfynd/A 33012-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2501,6 +2501,126 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>114700446</v>
+      </c>
+      <c r="B17" t="n">
+        <v>97528</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tomta, 2,1 km SV-ut (6), Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>654008</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6647999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C-Upp-0973</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2019-06-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ingvar Sundh</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Sjöström, Thorleif Joelson, Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33012-2021 artfynd.xlsx
+++ b/artfynd/A 33012-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33012-2021 artfynd.xlsx
+++ b/artfynd/A 33012-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2501,126 +2501,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>114700446</v>
-      </c>
-      <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Tomta, 2,1 km SV-ut (6), Upl</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>654008</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6647999</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Rasbo</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>C-Upp-0973</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2019-06-02</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2019-06-02</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Jörgen Sjöström, Thorleif Joelson, Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
